--- a/CRUD Table.xlsx
+++ b/CRUD Table.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\dyfry\workspace\2026\DAT602-Project\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{78A29904-BD89-43EF-8F45-3AC787E5A087}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D7903D01-0F3A-4948-B4F1-39D2F08BC0D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="830" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="974" uniqueCount="80">
   <si>
     <t>Account</t>
   </si>
@@ -253,6 +253,18 @@
   </si>
   <si>
     <t>___D</t>
+  </si>
+  <si>
+    <t>Player Join Room</t>
+  </si>
+  <si>
+    <t>Player Send Message</t>
+  </si>
+  <si>
+    <t>Create Room</t>
+  </si>
+  <si>
+    <t>C__</t>
   </si>
 </sst>
 </file>
@@ -632,7 +644,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Q62"/>
+  <dimension ref="A1:T62"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="18.109375" bestFit="1" customWidth="1"/>
@@ -652,9 +664,9 @@
     <col min="15" max="15" width="16.88671875" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="16.109375" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="18.6640625" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="10.77734375" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="12.44140625" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.6640625" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="15.109375" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="18.109375" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="11.77734375" bestFit="1" customWidth="1"/>
     <col min="21" max="21" width="13.6640625" bestFit="1" customWidth="1"/>
     <col min="22" max="22" width="9.21875" bestFit="1" customWidth="1"/>
     <col min="25" max="25" width="10.88671875" bestFit="1" customWidth="1"/>
@@ -676,12 +688,12 @@
     <col min="41" max="41" width="14.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="2" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>52</v>
       </c>
@@ -733,8 +745,17 @@
       <c r="Q2" s="6" t="s">
         <v>68</v>
       </c>
-    </row>
-    <row r="3" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="R2" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="S2" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="T2" s="6" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="3" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
         <v>51</v>
       </c>
@@ -754,8 +775,11 @@
       <c r="O3" s="1"/>
       <c r="P3" s="1"/>
       <c r="Q3" s="1"/>
-    </row>
-    <row r="4" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="R3" s="1"/>
+      <c r="S3" s="1"/>
+      <c r="T3" s="1"/>
+    </row>
+    <row r="4" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A4" s="3" t="s">
         <v>0</v>
       </c>
@@ -775,8 +799,11 @@
       <c r="O4" s="5"/>
       <c r="P4" s="5"/>
       <c r="Q4" s="5"/>
-    </row>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="R4" s="5"/>
+      <c r="S4" s="5"/>
+      <c r="T4" s="5"/>
+    </row>
+    <row r="5" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
         <v>16</v>
       </c>
@@ -828,8 +855,17 @@
       <c r="Q5" t="s">
         <v>70</v>
       </c>
-    </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="R5" t="s">
+        <v>69</v>
+      </c>
+      <c r="S5" t="s">
+        <v>70</v>
+      </c>
+      <c r="T5" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="6" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
         <v>1</v>
       </c>
@@ -881,8 +917,17 @@
       <c r="Q6" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="R6" t="s">
+        <v>70</v>
+      </c>
+      <c r="S6" t="s">
+        <v>70</v>
+      </c>
+      <c r="T6" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="7" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
         <v>2</v>
       </c>
@@ -934,8 +979,17 @@
       <c r="Q7" t="s">
         <v>71</v>
       </c>
-    </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="R7" t="s">
+        <v>70</v>
+      </c>
+      <c r="S7" t="s">
+        <v>70</v>
+      </c>
+      <c r="T7" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="8" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
         <v>3</v>
       </c>
@@ -987,8 +1041,17 @@
       <c r="Q8" t="s">
         <v>71</v>
       </c>
-    </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="R8" t="s">
+        <v>70</v>
+      </c>
+      <c r="S8" t="s">
+        <v>70</v>
+      </c>
+      <c r="T8" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="9" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
         <v>4</v>
       </c>
@@ -1040,8 +1103,17 @@
       <c r="Q9" t="s">
         <v>70</v>
       </c>
-    </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="R9" t="s">
+        <v>70</v>
+      </c>
+      <c r="S9" t="s">
+        <v>70</v>
+      </c>
+      <c r="T9" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="10" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A10" s="4" t="s">
         <v>5</v>
       </c>
@@ -1061,8 +1133,11 @@
       <c r="O10" s="5"/>
       <c r="P10" s="5"/>
       <c r="Q10" s="5"/>
-    </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="R10" s="5"/>
+      <c r="S10" s="5"/>
+      <c r="T10" s="5"/>
+    </row>
+    <row r="11" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A11" s="2" t="s">
         <v>19</v>
       </c>
@@ -1114,8 +1189,17 @@
       <c r="Q11" t="s">
         <v>70</v>
       </c>
-    </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="R11" t="s">
+        <v>74</v>
+      </c>
+      <c r="S11" t="s">
+        <v>69</v>
+      </c>
+      <c r="T11" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="12" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A12" s="2" t="s">
         <v>6</v>
       </c>
@@ -1167,8 +1251,17 @@
       <c r="Q12" t="s">
         <v>70</v>
       </c>
-    </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="R12" t="s">
+        <v>74</v>
+      </c>
+      <c r="S12" t="s">
+        <v>70</v>
+      </c>
+      <c r="T12" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="13" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A13" s="2" t="s">
         <v>7</v>
       </c>
@@ -1220,8 +1313,17 @@
       <c r="Q13" t="s">
         <v>70</v>
       </c>
-    </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="R13" t="s">
+        <v>74</v>
+      </c>
+      <c r="S13" t="s">
+        <v>70</v>
+      </c>
+      <c r="T13" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="14" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A14" s="2" t="s">
         <v>8</v>
       </c>
@@ -1273,8 +1375,17 @@
       <c r="Q14" t="s">
         <v>70</v>
       </c>
-    </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="R14" t="s">
+        <v>74</v>
+      </c>
+      <c r="S14" t="s">
+        <v>70</v>
+      </c>
+      <c r="T14" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="15" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A15" s="2" t="s">
         <v>9</v>
       </c>
@@ -1326,8 +1437,17 @@
       <c r="Q15" t="s">
         <v>70</v>
       </c>
-    </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="R15" t="s">
+        <v>74</v>
+      </c>
+      <c r="S15" t="s">
+        <v>70</v>
+      </c>
+      <c r="T15" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="16" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A16" s="2" t="s">
         <v>17</v>
       </c>
@@ -1379,8 +1499,17 @@
       <c r="Q16" t="s">
         <v>70</v>
       </c>
-    </row>
-    <row r="17" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="R16" t="s">
+        <v>74</v>
+      </c>
+      <c r="S16" t="s">
+        <v>70</v>
+      </c>
+      <c r="T16" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="17" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A17" s="2" t="s">
         <v>18</v>
       </c>
@@ -1432,8 +1561,17 @@
       <c r="Q17" t="s">
         <v>70</v>
       </c>
-    </row>
-    <row r="18" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="R17" t="s">
+        <v>74</v>
+      </c>
+      <c r="S17" t="s">
+        <v>70</v>
+      </c>
+      <c r="T17" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="18" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A18" s="5" t="s">
         <v>10</v>
       </c>
@@ -1453,8 +1591,11 @@
       <c r="O18" s="5"/>
       <c r="P18" s="5"/>
       <c r="Q18" s="5"/>
-    </row>
-    <row r="19" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="R18" s="5"/>
+      <c r="S18" s="5"/>
+      <c r="T18" s="5"/>
+    </row>
+    <row r="19" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A19" s="2" t="s">
         <v>20</v>
       </c>
@@ -1506,8 +1647,17 @@
       <c r="Q19" t="s">
         <v>70</v>
       </c>
-    </row>
-    <row r="20" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="R19" t="s">
+        <v>69</v>
+      </c>
+      <c r="S19" t="s">
+        <v>74</v>
+      </c>
+      <c r="T19" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="20" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A20" s="2" t="s">
         <v>21</v>
       </c>
@@ -1559,8 +1709,17 @@
       <c r="Q20" t="s">
         <v>70</v>
       </c>
-    </row>
-    <row r="21" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="R20" t="s">
+        <v>69</v>
+      </c>
+      <c r="S20" t="s">
+        <v>74</v>
+      </c>
+      <c r="T20" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="21" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A21" s="2" t="s">
         <v>11</v>
       </c>
@@ -1612,8 +1771,17 @@
       <c r="Q21" t="s">
         <v>70</v>
       </c>
-    </row>
-    <row r="22" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="R21" t="s">
+        <v>69</v>
+      </c>
+      <c r="S21" t="s">
+        <v>74</v>
+      </c>
+      <c r="T21" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="22" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A22" s="5" t="s">
         <v>12</v>
       </c>
@@ -1633,8 +1801,11 @@
       <c r="O22" s="5"/>
       <c r="P22" s="5"/>
       <c r="Q22" s="5"/>
-    </row>
-    <row r="23" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="R22" s="5"/>
+      <c r="S22" s="5"/>
+      <c r="T22" s="5"/>
+    </row>
+    <row r="23" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A23" s="2" t="s">
         <v>22</v>
       </c>
@@ -1686,8 +1857,17 @@
       <c r="Q23" t="s">
         <v>70</v>
       </c>
-    </row>
-    <row r="24" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="R23" t="s">
+        <v>69</v>
+      </c>
+      <c r="S23" t="s">
+        <v>70</v>
+      </c>
+      <c r="T23" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="24" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A24" s="2" t="s">
         <v>13</v>
       </c>
@@ -1739,8 +1919,17 @@
       <c r="Q24" t="s">
         <v>70</v>
       </c>
-    </row>
-    <row r="25" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="R24" t="s">
+        <v>69</v>
+      </c>
+      <c r="S24" t="s">
+        <v>70</v>
+      </c>
+      <c r="T24" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="25" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A25" s="5" t="s">
         <v>14</v>
       </c>
@@ -1760,8 +1949,11 @@
       <c r="O25" s="5"/>
       <c r="P25" s="5"/>
       <c r="Q25" s="5"/>
-    </row>
-    <row r="26" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="R25" s="5"/>
+      <c r="S25" s="5"/>
+      <c r="T25" s="5"/>
+    </row>
+    <row r="26" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A26" s="2" t="s">
         <v>50</v>
       </c>
@@ -1813,8 +2005,17 @@
       <c r="Q26" t="s">
         <v>70</v>
       </c>
-    </row>
-    <row r="27" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="R26" t="s">
+        <v>69</v>
+      </c>
+      <c r="S26" t="s">
+        <v>70</v>
+      </c>
+      <c r="T26" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="27" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A27" s="2" t="s">
         <v>20</v>
       </c>
@@ -1866,8 +2067,17 @@
       <c r="Q27" t="s">
         <v>70</v>
       </c>
-    </row>
-    <row r="28" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="R27" t="s">
+        <v>69</v>
+      </c>
+      <c r="S27" t="s">
+        <v>70</v>
+      </c>
+      <c r="T27" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="28" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A28" s="2" t="s">
         <v>23</v>
       </c>
@@ -1919,8 +2129,17 @@
       <c r="Q28" t="s">
         <v>70</v>
       </c>
-    </row>
-    <row r="29" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="R28" t="s">
+        <v>69</v>
+      </c>
+      <c r="S28" t="s">
+        <v>70</v>
+      </c>
+      <c r="T28" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="29" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A29" s="5" t="s">
         <v>15</v>
       </c>
@@ -1940,8 +2159,11 @@
       <c r="O29" s="5"/>
       <c r="P29" s="5"/>
       <c r="Q29" s="5"/>
-    </row>
-    <row r="30" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="R29" s="5"/>
+      <c r="S29" s="5"/>
+      <c r="T29" s="5"/>
+    </row>
+    <row r="30" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A30" s="2" t="s">
         <v>24</v>
       </c>
@@ -1993,8 +2215,17 @@
       <c r="Q30" t="s">
         <v>70</v>
       </c>
-    </row>
-    <row r="31" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="R30" t="s">
+        <v>69</v>
+      </c>
+      <c r="S30" t="s">
+        <v>70</v>
+      </c>
+      <c r="T30" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="31" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A31" s="2" t="s">
         <v>25</v>
       </c>
@@ -2046,8 +2277,17 @@
       <c r="Q31" t="s">
         <v>70</v>
       </c>
-    </row>
-    <row r="32" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="R31" t="s">
+        <v>69</v>
+      </c>
+      <c r="S31" t="s">
+        <v>70</v>
+      </c>
+      <c r="T31" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="32" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A32" s="2" t="s">
         <v>26</v>
       </c>
@@ -2099,8 +2339,17 @@
       <c r="Q32" t="s">
         <v>70</v>
       </c>
-    </row>
-    <row r="33" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="R32" t="s">
+        <v>69</v>
+      </c>
+      <c r="S32" t="s">
+        <v>70</v>
+      </c>
+      <c r="T32" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="33" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A33" s="2" t="s">
         <v>27</v>
       </c>
@@ -2152,8 +2401,17 @@
       <c r="Q33" t="s">
         <v>70</v>
       </c>
-    </row>
-    <row r="34" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="R33" t="s">
+        <v>69</v>
+      </c>
+      <c r="S33" t="s">
+        <v>70</v>
+      </c>
+      <c r="T33" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="34" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A34" s="5" t="s">
         <v>28</v>
       </c>
@@ -2173,8 +2431,11 @@
       <c r="O34" s="5"/>
       <c r="P34" s="5"/>
       <c r="Q34" s="5"/>
-    </row>
-    <row r="35" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="R34" s="5"/>
+      <c r="S34" s="5"/>
+      <c r="T34" s="5"/>
+    </row>
+    <row r="35" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A35" s="2" t="s">
         <v>23</v>
       </c>
@@ -2226,8 +2487,17 @@
       <c r="Q35" t="s">
         <v>70</v>
       </c>
-    </row>
-    <row r="36" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="R35" t="s">
+        <v>69</v>
+      </c>
+      <c r="S35" t="s">
+        <v>70</v>
+      </c>
+      <c r="T35" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="36" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A36" s="2" t="s">
         <v>50</v>
       </c>
@@ -2279,8 +2549,17 @@
       <c r="Q36" t="s">
         <v>70</v>
       </c>
-    </row>
-    <row r="37" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="R36" t="s">
+        <v>69</v>
+      </c>
+      <c r="S36" t="s">
+        <v>70</v>
+      </c>
+      <c r="T36" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="37" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A37" s="2" t="s">
         <v>29</v>
       </c>
@@ -2332,8 +2611,17 @@
       <c r="Q37" t="s">
         <v>70</v>
       </c>
-    </row>
-    <row r="38" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="R37" t="s">
+        <v>69</v>
+      </c>
+      <c r="S37" t="s">
+        <v>70</v>
+      </c>
+      <c r="T37" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="38" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A38" s="5" t="s">
         <v>30</v>
       </c>
@@ -2353,8 +2641,11 @@
       <c r="O38" s="5"/>
       <c r="P38" s="5"/>
       <c r="Q38" s="5"/>
-    </row>
-    <row r="39" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="R38" s="5"/>
+      <c r="S38" s="5"/>
+      <c r="T38" s="5"/>
+    </row>
+    <row r="39" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A39" s="2" t="s">
         <v>31</v>
       </c>
@@ -2406,8 +2697,17 @@
       <c r="Q39" t="s">
         <v>70</v>
       </c>
-    </row>
-    <row r="40" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="R39" t="s">
+        <v>69</v>
+      </c>
+      <c r="S39" t="s">
+        <v>70</v>
+      </c>
+      <c r="T39" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="40" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A40" s="2" t="s">
         <v>32</v>
       </c>
@@ -2459,8 +2759,17 @@
       <c r="Q40" t="s">
         <v>70</v>
       </c>
-    </row>
-    <row r="41" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="R40" t="s">
+        <v>69</v>
+      </c>
+      <c r="S40" t="s">
+        <v>70</v>
+      </c>
+      <c r="T40" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="41" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A41" s="2" t="s">
         <v>33</v>
       </c>
@@ -2512,8 +2821,17 @@
       <c r="Q41" t="s">
         <v>70</v>
       </c>
-    </row>
-    <row r="42" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="R41" t="s">
+        <v>69</v>
+      </c>
+      <c r="S41" t="s">
+        <v>70</v>
+      </c>
+      <c r="T41" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="42" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A42" s="2" t="s">
         <v>34</v>
       </c>
@@ -2565,8 +2883,17 @@
       <c r="Q42" t="s">
         <v>70</v>
       </c>
-    </row>
-    <row r="43" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="R42" t="s">
+        <v>69</v>
+      </c>
+      <c r="S42" t="s">
+        <v>70</v>
+      </c>
+      <c r="T42" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="43" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A43" s="2" t="s">
         <v>35</v>
       </c>
@@ -2618,8 +2945,17 @@
       <c r="Q43" t="s">
         <v>70</v>
       </c>
-    </row>
-    <row r="44" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="R43" t="s">
+        <v>69</v>
+      </c>
+      <c r="S43" t="s">
+        <v>70</v>
+      </c>
+      <c r="T43" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="44" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A44" s="2" t="s">
         <v>36</v>
       </c>
@@ -2671,8 +3007,17 @@
       <c r="Q44" t="s">
         <v>70</v>
       </c>
-    </row>
-    <row r="45" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="R44" t="s">
+        <v>69</v>
+      </c>
+      <c r="S44" t="s">
+        <v>70</v>
+      </c>
+      <c r="T44" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="45" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A45" s="2" t="s">
         <v>37</v>
       </c>
@@ -2724,8 +3069,17 @@
       <c r="Q45" t="s">
         <v>70</v>
       </c>
-    </row>
-    <row r="46" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="R45" t="s">
+        <v>69</v>
+      </c>
+      <c r="S45" t="s">
+        <v>70</v>
+      </c>
+      <c r="T45" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="46" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A46" s="2" t="s">
         <v>38</v>
       </c>
@@ -2777,8 +3131,17 @@
       <c r="Q46" t="s">
         <v>70</v>
       </c>
-    </row>
-    <row r="47" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="R46" t="s">
+        <v>69</v>
+      </c>
+      <c r="S46" t="s">
+        <v>70</v>
+      </c>
+      <c r="T46" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="47" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A47" s="5" t="s">
         <v>39</v>
       </c>
@@ -2798,8 +3161,11 @@
       <c r="O47" s="5"/>
       <c r="P47" s="5"/>
       <c r="Q47" s="5"/>
-    </row>
-    <row r="48" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="R47" s="5"/>
+      <c r="S47" s="5"/>
+      <c r="T47" s="5"/>
+    </row>
+    <row r="48" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A48" s="2" t="s">
         <v>40</v>
       </c>
@@ -2851,8 +3217,17 @@
       <c r="Q48" t="s">
         <v>70</v>
       </c>
-    </row>
-    <row r="49" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="R48" t="s">
+        <v>69</v>
+      </c>
+      <c r="S48" t="s">
+        <v>70</v>
+      </c>
+      <c r="T48" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="49" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A49" s="2" t="s">
         <v>29</v>
       </c>
@@ -2904,8 +3279,17 @@
       <c r="Q49" t="s">
         <v>70</v>
       </c>
-    </row>
-    <row r="50" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="R49" t="s">
+        <v>69</v>
+      </c>
+      <c r="S49" t="s">
+        <v>70</v>
+      </c>
+      <c r="T49" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="50" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A50" s="2" t="s">
         <v>20</v>
       </c>
@@ -2957,8 +3341,17 @@
       <c r="Q50" t="s">
         <v>70</v>
       </c>
-    </row>
-    <row r="51" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="R50" t="s">
+        <v>69</v>
+      </c>
+      <c r="S50" t="s">
+        <v>70</v>
+      </c>
+      <c r="T50" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="51" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A51" s="2" t="s">
         <v>41</v>
       </c>
@@ -3010,8 +3403,17 @@
       <c r="Q51" t="s">
         <v>70</v>
       </c>
-    </row>
-    <row r="52" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="R51" t="s">
+        <v>69</v>
+      </c>
+      <c r="S51" t="s">
+        <v>70</v>
+      </c>
+      <c r="T51" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="52" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A52" s="5" t="s">
         <v>43</v>
       </c>
@@ -3031,8 +3433,11 @@
       <c r="O52" s="5"/>
       <c r="P52" s="5"/>
       <c r="Q52" s="5"/>
-    </row>
-    <row r="53" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="R52" s="5"/>
+      <c r="S52" s="5"/>
+      <c r="T52" s="5"/>
+    </row>
+    <row r="53" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A53" s="2" t="s">
         <v>29</v>
       </c>
@@ -3084,8 +3489,17 @@
       <c r="Q53" t="s">
         <v>70</v>
       </c>
-    </row>
-    <row r="54" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="R53" t="s">
+        <v>69</v>
+      </c>
+      <c r="S53" t="s">
+        <v>70</v>
+      </c>
+      <c r="T53" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="54" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A54" s="2" t="s">
         <v>44</v>
       </c>
@@ -3137,8 +3551,17 @@
       <c r="Q54" t="s">
         <v>70</v>
       </c>
-    </row>
-    <row r="55" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="R54" t="s">
+        <v>69</v>
+      </c>
+      <c r="S54" t="s">
+        <v>70</v>
+      </c>
+      <c r="T54" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="55" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A55" s="2" t="s">
         <v>45</v>
       </c>
@@ -3190,8 +3613,17 @@
       <c r="Q55" t="s">
         <v>70</v>
       </c>
-    </row>
-    <row r="56" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="R55" t="s">
+        <v>69</v>
+      </c>
+      <c r="S55" t="s">
+        <v>70</v>
+      </c>
+      <c r="T55" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="56" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A56" s="5" t="s">
         <v>46</v>
       </c>
@@ -3211,8 +3643,11 @@
       <c r="O56" s="5"/>
       <c r="P56" s="5"/>
       <c r="Q56" s="5"/>
-    </row>
-    <row r="57" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="R56" s="5"/>
+      <c r="S56" s="5"/>
+      <c r="T56" s="5"/>
+    </row>
+    <row r="57" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A57" s="2" t="s">
         <v>47</v>
       </c>
@@ -3264,8 +3699,17 @@
       <c r="Q57" t="s">
         <v>70</v>
       </c>
-    </row>
-    <row r="58" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="R57" t="s">
+        <v>69</v>
+      </c>
+      <c r="S57" t="s">
+        <v>70</v>
+      </c>
+      <c r="T57" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="58" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A58" s="2" t="s">
         <v>48</v>
       </c>
@@ -3317,8 +3761,17 @@
       <c r="Q58" t="s">
         <v>70</v>
       </c>
-    </row>
-    <row r="59" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="R58" t="s">
+        <v>69</v>
+      </c>
+      <c r="S58" t="s">
+        <v>70</v>
+      </c>
+      <c r="T58" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="59" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A59" s="5" t="s">
         <v>49</v>
       </c>
@@ -3338,8 +3791,11 @@
       <c r="O59" s="5"/>
       <c r="P59" s="5"/>
       <c r="Q59" s="5"/>
-    </row>
-    <row r="60" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="R59" s="5"/>
+      <c r="S59" s="5"/>
+      <c r="T59" s="5"/>
+    </row>
+    <row r="60" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A60" s="2" t="s">
         <v>44</v>
       </c>
@@ -3391,8 +3847,17 @@
       <c r="Q60" t="s">
         <v>70</v>
       </c>
-    </row>
-    <row r="61" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="R60" t="s">
+        <v>73</v>
+      </c>
+      <c r="S60" t="s">
+        <v>70</v>
+      </c>
+      <c r="T60" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="61" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A61" s="2" t="s">
         <v>20</v>
       </c>
@@ -3444,8 +3909,17 @@
       <c r="Q61" t="s">
         <v>70</v>
       </c>
-    </row>
-    <row r="62" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="R61" t="s">
+        <v>73</v>
+      </c>
+      <c r="S61" t="s">
+        <v>70</v>
+      </c>
+      <c r="T61" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="62" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A62" s="2" t="s">
         <v>33</v>
       </c>
@@ -3495,6 +3969,15 @@
         <v>75</v>
       </c>
       <c r="Q62" t="s">
+        <v>70</v>
+      </c>
+      <c r="R62" t="s">
+        <v>73</v>
+      </c>
+      <c r="S62" t="s">
+        <v>70</v>
+      </c>
+      <c r="T62" t="s">
         <v>70</v>
       </c>
     </row>
